--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
@@ -42,19 +42,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>Row Labels</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sum of Sold</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cake</x:t>
   </x:si>
   <x:si>
     <x:t>Pie</x:t>
   </x:si>
   <x:si>
+    <x:t>Row Labels</x:t>
+  </x:si>
+  <x:si>
     <x:t>Grand Total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sum of Sold</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -514,15 +514,15 @@
   <x:sheetData>
     <x:row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <x:c r="A3" s="0" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <x:c r="A4" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B4" s="0">
         <x:v>16</x:v>
@@ -530,7 +530,7 @@
     </x:row>
     <x:row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <x:c r="A5" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="0">
         <x:v>7</x:v>
@@ -538,7 +538,7 @@
     </x:row>
     <x:row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <x:c r="A6" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0">
         <x:v>23</x:v>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
@@ -502,21 +502,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{BA14C63C-6F7B-4D56-BFA1-7A2D005FF6C4}" mc:Ignorable="x14ac xr xr2 xr3">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A3:B6"/>
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.140625" style="0" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="11.425781" style="0" bestFit="1" customWidth="1"/>
+    <x:col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="11.425781" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="A3" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="B3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -524,7 +521,7 @@
       <x:c r="A4" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B4" s="0">
+      <x:c r="B4">
         <x:v>16</x:v>
       </x:c>
     </x:row>
@@ -532,7 +529,7 @@
       <x:c r="A5" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B5" s="0">
+      <x:c r="B5">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -540,15 +537,11 @@
       <x:c r="A6" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="0">
+      <x:c r="B6">
         <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/PivotTableWithoutSourceData-output.xlsx
@@ -506,7 +506,7 @@
   <x:sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
     <x:col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <x:col min="2" max="2" width="11.425781" bestFit="1" customWidth="1"/>
+    <x:col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:2" x14ac:dyDescent="0.25">
